--- a/artfynd/A 40509-2022 artfynd.xlsx
+++ b/artfynd/A 40509-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40509-2022 artfynd.xlsx
+++ b/artfynd/A 40509-2022 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>119719397</v>
       </c>
       <c r="B4" t="n">
-        <v>100080</v>
+        <v>100103</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 40509-2022 artfynd.xlsx
+++ b/artfynd/A 40509-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112610713</v>
+        <v>119652989</v>
       </c>
       <c r="B2" t="n">
-        <v>108802</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221049</v>
+        <v>1012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Skogslysing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Valeriana dioica</t>
+          <t>Lysimachia nemorum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +704,23 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hörröd, Sk</t>
+          <t>Hörröds utmark 2:54-3, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440509</v>
+        <v>440537</v>
       </c>
       <c r="R2" t="n">
-        <v>6181815</v>
+        <v>6181870</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,33 +758,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Stoltze</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Martin Stoltze</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119652989</v>
+        <v>112610712</v>
       </c>
       <c r="B3" t="n">
-        <v>104892</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1012</v>
+        <v>220075</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogslysing</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lysimachia nemorum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -816,23 +806,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hörröds utmark 2:54-3, Sk</t>
+          <t>Hörröd, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440537</v>
+        <v>440516</v>
       </c>
       <c r="R3" t="n">
-        <v>6181870</v>
+        <v>6181781</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,12 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2023-05-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,51 +861,45 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Stoltze</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119719397</v>
+        <v>112610713</v>
       </c>
       <c r="B4" t="n">
-        <v>100103</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>221049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Valeriana dioica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -923,27 +908,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hörröds utmark 2:54-3, Sk</t>
+          <t>Hörröd, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440537</v>
+        <v>440509</v>
       </c>
       <c r="R4" t="n">
-        <v>6181870</v>
+        <v>6181815</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,17 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Enstaka blad</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,22 +963,132 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119719397</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hörröds utmark 2:54-3, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>440537</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6181870</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hörröd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka blad</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Martin Stoltze</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Martin Stoltze</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40509-2022 artfynd.xlsx
+++ b/artfynd/A 40509-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119652989</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610712</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610713</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,8 +1109,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119719397</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>